--- a/config/gem/gem.xlsx
+++ b/config/gem/gem.xlsx
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>強撃</t>
+          <t>强击</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10201,7 +10201,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -11461,7 +11461,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -11979,7 +11979,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>好戦</t>
+          <t>好战</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>攻撃ルーン</t>
+          <t>攻击符文</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -13904,7 +13904,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -14138,7 +14138,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -14382,7 +14382,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -15261,7 +15261,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -15505,7 +15505,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -16379,7 +16379,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -17360,7 +17360,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -17487,7 +17487,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -17604,7 +17604,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -17955,7 +17955,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -18082,7 +18082,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -18331,7 +18331,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -18829,7 +18829,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -18961,7 +18961,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -19205,7 +19205,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -19449,7 +19449,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -19713,7 +19713,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -19835,7 +19835,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -19957,7 +19957,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -20079,7 +20079,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -20201,7 +20201,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -20333,7 +20333,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -20425,14 +20425,14 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D155" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -20465,7 +20465,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -20542,14 +20542,14 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D156" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -20659,14 +20659,14 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D157" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -20699,7 +20699,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -20776,14 +20776,14 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D158" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -20816,7 +20816,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -20893,14 +20893,14 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D159" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -20933,7 +20933,7 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -21020,14 +21020,14 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D160" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -21060,7 +21060,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -21147,14 +21147,14 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D161" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -21187,7 +21187,7 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -21264,14 +21264,14 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D162" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -21304,7 +21304,7 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -21381,14 +21381,14 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D163" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -21421,7 +21421,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -21498,14 +21498,14 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D164" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -21538,7 +21538,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -21615,14 +21615,14 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D165" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -21655,7 +21655,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -21742,14 +21742,14 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D166" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -21869,14 +21869,14 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D167" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -21909,7 +21909,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -21991,14 +21991,14 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D168" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -22031,7 +22031,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -22113,14 +22113,14 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D169" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -22153,7 +22153,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -22235,14 +22235,14 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D170" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -22275,7 +22275,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -22357,14 +22357,14 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D171" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -22489,14 +22489,14 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D172" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -22529,7 +22529,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -22621,14 +22621,14 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D173" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -22661,7 +22661,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -22743,14 +22743,14 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D174" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -22783,7 +22783,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -22865,14 +22865,14 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D175" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -22905,7 +22905,7 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -22987,14 +22987,14 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D176" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -23109,14 +23109,14 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D177" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -23149,7 +23149,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -23241,14 +23241,14 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D178" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -23281,7 +23281,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -23373,14 +23373,14 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D179" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -23413,7 +23413,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -23495,14 +23495,14 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D180" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -23535,7 +23535,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -23617,14 +23617,14 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D181" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -23657,7 +23657,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -23739,14 +23739,14 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D182" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -23861,14 +23861,14 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D183" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -23901,7 +23901,7 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -23993,14 +23993,14 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
+          <t>金刚</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
           <t>金剛</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>金剛</t>
-        </is>
-      </c>
       <c r="D184" t="inlineStr">
         <is>
           <t>Adamant</t>
@@ -24033,7 +24033,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>防御ルーン</t>
+          <t>防御符文</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -24125,7 +24125,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>加護</t>
+          <t>照壁</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -24165,7 +24165,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -24242,7 +24242,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>加護</t>
+          <t>照壁</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -24282,7 +24282,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>加護</t>
+          <t>照壁</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -24409,7 +24409,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -24496,7 +24496,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>加護</t>
+          <t>照壁</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -24536,7 +24536,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -24613,7 +24613,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>加護</t>
+          <t>照壁</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -24653,7 +24653,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -24740,7 +24740,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>加護</t>
+          <t>照壁</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -24867,7 +24867,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>加護</t>
+          <t>照壁</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -24907,7 +24907,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -24989,7 +24989,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>加護</t>
+          <t>照壁</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -25029,7 +25029,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -25121,7 +25121,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>加護</t>
+          <t>照壁</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -25253,7 +25253,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>加護</t>
+          <t>照壁</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -25293,7 +25293,7 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>加護</t>
+          <t>照壁</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -25415,7 +25415,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -25507,7 +25507,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>加護</t>
+          <t>照壁</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -25547,7 +25547,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -25639,7 +25639,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>加護</t>
+          <t>照壁</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -25679,7 +25679,7 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -25761,7 +25761,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>加護</t>
+          <t>照壁</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -25801,7 +25801,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>加護</t>
+          <t>照壁</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -25933,7 +25933,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -26065,7 +26065,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -26142,7 +26142,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -26182,7 +26182,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -26269,7 +26269,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -26309,7 +26309,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -26396,7 +26396,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -26436,7 +26436,7 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -26513,7 +26513,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -26553,7 +26553,7 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -26640,7 +26640,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -26680,7 +26680,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -26767,7 +26767,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -26807,7 +26807,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -26889,7 +26889,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -26929,7 +26929,7 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -27021,7 +27021,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -27061,7 +27061,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -27153,7 +27153,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -27193,7 +27193,7 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -27275,7 +27275,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -27407,7 +27407,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -27447,7 +27447,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -27539,7 +27539,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -27579,7 +27579,7 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -27661,7 +27661,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -27701,7 +27701,7 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -27793,7 +27793,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>閃光</t>
+          <t>闪光</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -27833,7 +27833,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -27925,7 +27925,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -27965,7 +27965,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -28042,7 +28042,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -28082,7 +28082,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -28159,7 +28159,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -28199,7 +28199,7 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -28276,7 +28276,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -28316,7 +28316,7 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -28393,7 +28393,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -28433,7 +28433,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -28510,7 +28510,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -28550,7 +28550,7 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -28627,7 +28627,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -28667,7 +28667,7 @@
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -28749,7 +28749,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -28789,7 +28789,7 @@
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -28871,7 +28871,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -28993,7 +28993,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -29033,7 +29033,7 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -29115,7 +29115,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -29155,7 +29155,7 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -29237,7 +29237,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -29277,7 +29277,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -29359,7 +29359,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -29399,7 +29399,7 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -29521,7 +29521,7 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -29603,7 +29603,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>報復</t>
+          <t>报复</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -29643,7 +29643,7 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>補助ルーン</t>
+          <t>辅助符文</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
